--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7784,0.0518,0.0834,0.0826</t>
-  </si>
-  <si>
-    <t>0.7703,0.0569,0.0164,0.0631</t>
-  </si>
-  <si>
-    <t>0.5155,0.0172,0.0094,0.4894</t>
-  </si>
-  <si>
-    <t>0.8687,0.0225,0.0032,0.0236</t>
-  </si>
-  <si>
-    <t>0.7687,0.1220,0.0135,0.0189</t>
-  </si>
-  <si>
-    <t>0.6437,0.0616,0.0074,0.0672</t>
-  </si>
-  <si>
-    <t>0.8753,0.0230,0.0041,0.0247</t>
-  </si>
-  <si>
-    <t>0.5887,0.1228,0.0098,0.0512</t>
-  </si>
-  <si>
-    <t>0.6908,0.0823,0.0216,0.0799</t>
-  </si>
-  <si>
-    <t>0.6904,0.1738,0.0119,0.0176</t>
-  </si>
-  <si>
-    <t>0.8606,0.0430,0.0046,0.0168</t>
-  </si>
-  <si>
-    <t>0.7844,0.0463,0.0063,0.0343</t>
-  </si>
-  <si>
-    <t>0.7210,0.0627,0.0776,0.0903</t>
-  </si>
-  <si>
-    <t>0.7441,0.1111,0.0967,0.0483</t>
-  </si>
-  <si>
-    <t>0.9371,0.0077,0.0166,0.0121</t>
-  </si>
-  <si>
-    <t>0.6679,0.2033,0.1497,0.0098</t>
-  </si>
-  <si>
-    <t>0.7253,0.0781,0.0206,0.0705</t>
-  </si>
-  <si>
-    <t>0.0091,0.9698,0.0552,0.0238</t>
-  </si>
-  <si>
-    <t>0.1832,0.7672,0.0516,0.0118</t>
-  </si>
-  <si>
-    <t>0.6969,0.2372,0.0128,0.0077</t>
-  </si>
-  <si>
-    <t>0.0365,0.9519,0.0283,0.0080</t>
-  </si>
-  <si>
-    <t>0.4966,0.4846,0.0127,0.0041</t>
-  </si>
-  <si>
-    <t>0.9286,0.0138,0.0202,0.0084</t>
-  </si>
-  <si>
-    <t>0.8841,0.0195,0.0336,0.0323</t>
-  </si>
-  <si>
-    <t>0.8220,0.0111,0.1799,0.0126</t>
-  </si>
-  <si>
-    <t>0.6643,0.1721,0.0808,0.0474</t>
-  </si>
-  <si>
-    <t>0.5169,0.0174,0.5550,0.0114</t>
-  </si>
-  <si>
-    <t>0.8789,0.0154,0.0463,0.0357</t>
-  </si>
-  <si>
-    <t>0.7111,0.0434,0.3109,0.0166</t>
-  </si>
-  <si>
-    <t>0.3600,0.6103,0.0256,0.0114</t>
-  </si>
-  <si>
-    <t>0.7666,0.0799,0.0183,0.0370</t>
-  </si>
-  <si>
-    <t>0.0416,0.6767,0.8487,0.0124</t>
-  </si>
-  <si>
-    <t>0.8333,0.0769,0.0152,0.0161</t>
-  </si>
-  <si>
-    <t>0.6585,0.1805,0.0213,0.0292</t>
-  </si>
-  <si>
-    <t>0.5768,0.3113,0.0548,0.0290</t>
-  </si>
-  <si>
-    <t>0.7626,0.0956,0.0075,0.0214</t>
-  </si>
-  <si>
-    <t>0.2689,0.4976,0.0482,0.0473</t>
-  </si>
-  <si>
-    <t>0.5930,0.0436,0.3046,0.0476</t>
-  </si>
-  <si>
-    <t>0.6675,0.0115,0.2763,0.0381</t>
-  </si>
-  <si>
-    <t>0.8672,0.0110,0.1215,0.0071</t>
-  </si>
-  <si>
-    <t>0.8871,0.0137,0.0749,0.0179</t>
-  </si>
-  <si>
-    <t>0.6022,0.1067,0.2501,0.0503</t>
-  </si>
-  <si>
-    <t>0.3384,0.6816,0.0315,0.0080</t>
-  </si>
-  <si>
-    <t>0.7032,0.0358,0.3147,0.0140</t>
-  </si>
-  <si>
-    <t>0.7069,0.1624,0.0146,0.0205</t>
-  </si>
-  <si>
-    <t>0.3634,0.4351,0.0092,0.0171</t>
-  </si>
-  <si>
-    <t>0.0755,0.8796,0.0636,0.0164</t>
-  </si>
-  <si>
-    <t>0.5512,0.2285,0.0218,0.0303</t>
-  </si>
-  <si>
-    <t>0.1435,0.0871,0.8053,0.0273</t>
-  </si>
-  <si>
-    <t>0.3567,0.2939,0.3815,0.0031</t>
-  </si>
-  <si>
-    <t>0.6697,0.0453,0.2640,0.0392</t>
-  </si>
-  <si>
-    <t>0.1913,0.0742,0.8728,0.0040</t>
-  </si>
-  <si>
-    <t>0.0218,0.6124,0.9512,0.0023</t>
-  </si>
-  <si>
-    <t>0.5521,0.0944,0.4679,0.0055</t>
-  </si>
-  <si>
-    <t>0.7373,0.0756,0.0128,0.0435</t>
-  </si>
-  <si>
-    <t>0.9083,0.0435,0.0012,0.0034</t>
-  </si>
-  <si>
-    <t>0.8407,0.0511,0.0083,0.0238</t>
-  </si>
-  <si>
-    <t>0.1168,0.6426,0.6666,0.0187</t>
-  </si>
-  <si>
-    <t>0.6806,0.0974,0.0099,0.0477</t>
-  </si>
-  <si>
-    <t>0.8549,0.0377,0.0056,0.0212</t>
-  </si>
-  <si>
-    <t>0.5922,0.1195,0.0254,0.0973</t>
-  </si>
-  <si>
-    <t>0.1259,0.1312,0.8805,0.0044</t>
-  </si>
-  <si>
-    <t>0.3215,0.0471,0.7623,0.0054</t>
-  </si>
-  <si>
-    <t>0.5715,0.1446,0.3354,0.0063</t>
-  </si>
-  <si>
-    <t>0.0230,0.8040,0.8634,0.0019</t>
-  </si>
-  <si>
-    <t>0.0495,0.0823,0.9537,0.0017</t>
-  </si>
-  <si>
-    <t>0.2669,0.6564,0.0261,0.0122</t>
-  </si>
-  <si>
-    <t>0.0048,0.9904,0.0313,0.0046</t>
-  </si>
-  <si>
-    <t>0.8950,0.0474,0.0050,0.0108</t>
-  </si>
-  <si>
-    <t>0.1575,0.5776,0.5223,0.0652</t>
-  </si>
-  <si>
-    <t>0.1090,0.5429,0.7812,0.0210</t>
-  </si>
-  <si>
-    <t>0.0948,0.6584,0.6374,0.0051</t>
-  </si>
-  <si>
-    <t>0.5052,0.1531,0.3385,0.0320</t>
-  </si>
-  <si>
-    <t>0.0029,0.9770,0.7973,0.0010</t>
-  </si>
-  <si>
-    <t>0.0044,0.8786,0.9582,0.0011</t>
-  </si>
-  <si>
-    <t>0.7598,0.0133,0.0175,0.2061</t>
-  </si>
-  <si>
-    <t>0.7606,0.0275,0.0064,0.1050</t>
-  </si>
-  <si>
-    <t>0.9097,0.0053,0.0013,0.0437</t>
-  </si>
-  <si>
-    <t>0.6538,0.1380,0.0361,0.0723</t>
-  </si>
-  <si>
-    <t>0.7579,0.0374,0.0318,0.1228</t>
-  </si>
-  <si>
-    <t>0.8859,0.0117,0.0066,0.0710</t>
-  </si>
-  <si>
-    <t>0.2677,0.5150,0.3712,0.0173</t>
-  </si>
-  <si>
-    <t>0.0037,0.9558,0.8895,0.0019</t>
-  </si>
-  <si>
-    <t>0.6507,0.0267,0.3635,0.0178</t>
-  </si>
-  <si>
-    <t>0.1233,0.2761,0.8076,0.0121</t>
-  </si>
-  <si>
-    <t>0.2653,0.5165,0.4067,0.0147</t>
-  </si>
-  <si>
-    <t>0.1385,0.7283,0.4087,0.0061</t>
-  </si>
-  <si>
-    <t>0.8340,0.0256,0.0047,0.0409</t>
-  </si>
-  <si>
-    <t>0.8558,0.0534,0.0038,0.0105</t>
-  </si>
-  <si>
-    <t>0.6453,0.1015,0.0093,0.0452</t>
-  </si>
-  <si>
-    <t>0.5682,0.1927,0.0349,0.0532</t>
-  </si>
-  <si>
-    <t>0.9017,0.0223,0.0032,0.0150</t>
-  </si>
-  <si>
-    <t>0.7319,0.0574,0.0070,0.0333</t>
-  </si>
-  <si>
-    <t>0.7785,0.0660,0.0066,0.0203</t>
-  </si>
-  <si>
-    <t>0.5809,0.3137,0.0202,0.0160</t>
-  </si>
-  <si>
-    <t>0.8695,0.0307,0.0035,0.0165</t>
-  </si>
-  <si>
-    <t>0.7241,0.1705,0.0256,0.0191</t>
-  </si>
-  <si>
-    <t>0.7876,0.0640,0.0110,0.0363</t>
-  </si>
-  <si>
-    <t>0.4171,0.2973,0.0158,0.0343</t>
-  </si>
-  <si>
-    <t>0.8644,0.0441,0.0052,0.0114</t>
-  </si>
-  <si>
-    <t>0.8099,0.0386,0.0062,0.0365</t>
-  </si>
-  <si>
-    <t>0.8142,0.0880,0.0052,0.0115</t>
-  </si>
-  <si>
-    <t>0.6477,0.1287,0.0255,0.0530</t>
-  </si>
-  <si>
-    <t>0.2513,0.1747,0.7209,0.0100</t>
-  </si>
-  <si>
-    <t>0.8350,0.0209,0.1477,0.0111</t>
-  </si>
-  <si>
-    <t>0.9058,0.0232,0.0207,0.0178</t>
-  </si>
-  <si>
-    <t>0.7207,0.0969,0.1641,0.0283</t>
-  </si>
-  <si>
-    <t>0.0053,0.9868,0.0169,0.0029</t>
-  </si>
-  <si>
-    <t>0.1004,0.8575,0.0350,0.0100</t>
-  </si>
-  <si>
-    <t>0.5402,0.3502,0.0165,0.0130</t>
-  </si>
-  <si>
-    <t>0.4137,0.3806,0.0223,0.0283</t>
-  </si>
-  <si>
-    <t>0.6221,0.1913,0.0094,0.0182</t>
-  </si>
-  <si>
-    <t>0.0198,0.9610,0.0703,0.0138</t>
-  </si>
-  <si>
-    <t>0.6909,0.1619,0.0095,0.0182</t>
-  </si>
-  <si>
-    <t>0.8881,0.0242,0.0088,0.0233</t>
-  </si>
-  <si>
-    <t>0.8833,0.0337,0.0119,0.0199</t>
-  </si>
-  <si>
-    <t>0.8429,0.0808,0.0260,0.0151</t>
-  </si>
-  <si>
-    <t>0.5277,0.2309,0.1958,0.0432</t>
-  </si>
-  <si>
-    <t>0.7141,0.0934,0.0289,0.0658</t>
-  </si>
-  <si>
-    <t>0.5743,0.2619,0.0305,0.0258</t>
-  </si>
-  <si>
-    <t>0.1553,0.7618,0.0219,0.0259</t>
-  </si>
-  <si>
-    <t>0.6046,0.1330,0.0325,0.0619</t>
-  </si>
-  <si>
-    <t>0.0823,0.9242,0.0224,0.0046</t>
-  </si>
-  <si>
-    <t>0.7812,0.1967,0.0120,0.0047</t>
-  </si>
-  <si>
-    <t>0.5141,0.3457,0.0117,0.0129</t>
-  </si>
-  <si>
-    <t>0.3894,0.1980,0.0180,0.1082</t>
-  </si>
-  <si>
-    <t>0.8489,0.0468,0.0104,0.0243</t>
-  </si>
-  <si>
-    <t>0.7911,0.0682,0.0063,0.0229</t>
-  </si>
-  <si>
-    <t>0.6811,0.1151,0.0191,0.0319</t>
-  </si>
-  <si>
-    <t>0.5852,0.1419,0.0422,0.0873</t>
-  </si>
-  <si>
-    <t>0.8095,0.0339,0.0037,0.0268</t>
-  </si>
-  <si>
-    <t>0.8915,0.0299,0.0038,0.0140</t>
-  </si>
-  <si>
-    <t>0.7968,0.0733,0.0110,0.0311</t>
-  </si>
-  <si>
-    <t>0.8318,0.0287,0.0099,0.0568</t>
-  </si>
-  <si>
-    <t>0.5395,0.0756,0.4678,0.0086</t>
-  </si>
-  <si>
-    <t>0.5473,0.2263,0.2827,0.0156</t>
-  </si>
-  <si>
-    <t>0.1879,0.2507,0.7605,0.0087</t>
-  </si>
-  <si>
-    <t>0.3555,0.0201,0.7263,0.0046</t>
-  </si>
-  <si>
-    <t>0.8927,0.0267,0.0075,0.0229</t>
-  </si>
-  <si>
-    <t>0.9188,0.0140,0.0228,0.0123</t>
-  </si>
-  <si>
-    <t>0.9243,0.0160,0.0373,0.0097</t>
-  </si>
-  <si>
-    <t>0.8058,0.0336,0.0165,0.0556</t>
-  </si>
-  <si>
-    <t>0.7280,0.0839,0.0431,0.0677</t>
-  </si>
-  <si>
-    <t>0.6623,0.0239,0.0099,0.2730</t>
-  </si>
-  <si>
-    <t>0.8692,0.0116,0.0042,0.0729</t>
-  </si>
-  <si>
-    <t>0.8352,0.0272,0.0164,0.0604</t>
-  </si>
-  <si>
-    <t>0.0070,0.9751,0.5618,0.0060</t>
-  </si>
-  <si>
-    <t>0.9083,0.0151,0.0029,0.0253</t>
-  </si>
-  <si>
-    <t>0.3895,0.5561,0.0418,0.0133</t>
-  </si>
-  <si>
-    <t>0.8097,0.0524,0.0069,0.0273</t>
-  </si>
-  <si>
-    <t>0.8300,0.0648,0.0062,0.0122</t>
-  </si>
-  <si>
-    <t>0.8650,0.0446,0.0119,0.0237</t>
-  </si>
-  <si>
-    <t>0.9298,0.0056,0.0029,0.0344</t>
-  </si>
-  <si>
-    <t>0.6388,0.1960,0.0067,0.0138</t>
-  </si>
-  <si>
-    <t>0.1042,0.6352,0.7024,0.0245</t>
-  </si>
-  <si>
-    <t>0.9435,0.0070,0.0033,0.0184</t>
-  </si>
-  <si>
-    <t>0.9056,0.0278,0.0055,0.0147</t>
-  </si>
-  <si>
-    <t>0.7224,0.1284,0.0175,0.0250</t>
-  </si>
-  <si>
-    <t>0.7868,0.0871,0.0115,0.0179</t>
-  </si>
-  <si>
-    <t>0.8610,0.0436,0.0092,0.0192</t>
-  </si>
-  <si>
-    <t>0.6126,0.0473,0.0171,0.1817</t>
-  </si>
-  <si>
-    <t>0.6879,0.2410,0.0598,0.0151</t>
-  </si>
-  <si>
-    <t>0.8024,0.0904,0.0257,0.0204</t>
-  </si>
-  <si>
-    <t>0.8259,0.0761,0.0067,0.0118</t>
-  </si>
-  <si>
-    <t>0.6769,0.0986,0.0152,0.0588</t>
-  </si>
-  <si>
-    <t>0.7239,0.0990,0.0110,0.0295</t>
-  </si>
-  <si>
-    <t>0.7281,0.0347,0.0075,0.1029</t>
-  </si>
-  <si>
-    <t>0.8329,0.0923,0.0086,0.0131</t>
-  </si>
-  <si>
-    <t>0.7311,0.0696,0.0103,0.0466</t>
-  </si>
-  <si>
-    <t>0.8458,0.0294,0.0052,0.0386</t>
-  </si>
-  <si>
-    <t>0.7951,0.0273,0.0075,0.0778</t>
-  </si>
-  <si>
-    <t>0.3202,0.4602,0.0333,0.0318</t>
-  </si>
-  <si>
-    <t>0.8451,0.0399,0.0029,0.0180</t>
-  </si>
-  <si>
-    <t>0.3372,0.4549,0.0155,0.0322</t>
-  </si>
-  <si>
-    <t>0.8511,0.0492,0.0038,0.0103</t>
-  </si>
-  <si>
-    <t>0.7051,0.0860,0.0067,0.0351</t>
-  </si>
-  <si>
-    <t>0.8812,0.0501,0.0023,0.0063</t>
-  </si>
-  <si>
-    <t>0.8795,0.0740,0.0039,0.0053</t>
-  </si>
-  <si>
-    <t>0.7839,0.1378,0.0134,0.0151</t>
-  </si>
-  <si>
-    <t>0.0038,0.8177,0.9744,0.0012</t>
-  </si>
-  <si>
-    <t>0.6424,0.2882,0.0094,0.0080</t>
-  </si>
-  <si>
-    <t>0.5981,0.0474,0.4810,0.0091</t>
-  </si>
-  <si>
-    <t>0.7037,0.1116,0.2024,0.0160</t>
-  </si>
-  <si>
-    <t>0.7243,0.0465,0.2995,0.0112</t>
-  </si>
-  <si>
-    <t>0.2149,0.5713,0.4541,0.0158</t>
-  </si>
-  <si>
-    <t>0.7102,0.0186,0.3542,0.0090</t>
-  </si>
-  <si>
-    <t>0.3003,0.0445,0.7769,0.0058</t>
-  </si>
-  <si>
-    <t>0.4352,0.0057,0.7707,0.0021</t>
-  </si>
-  <si>
-    <t>0.6483,0.0644,0.3212,0.0287</t>
-  </si>
-  <si>
-    <t>0.5079,0.0473,0.5341,0.0196</t>
-  </si>
-  <si>
-    <t>0.6840,0.2045,0.0551,0.0132</t>
-  </si>
-  <si>
-    <t>0.8990,0.0398,0.0312,0.0098</t>
-  </si>
-  <si>
-    <t>0.8269,0.0446,0.0240,0.0424</t>
-  </si>
-  <si>
-    <t>0.8352,0.1138,0.0155,0.0073</t>
-  </si>
-  <si>
-    <t>0.8704,0.0233,0.0435,0.0382</t>
-  </si>
-  <si>
-    <t>0.8269,0.0481,0.0332,0.0507</t>
-  </si>
-  <si>
-    <t>0.7081,0.1377,0.0116,0.0196</t>
-  </si>
-  <si>
-    <t>0.5281,0.4249,0.0059,0.0058</t>
-  </si>
-  <si>
-    <t>0.7132,0.1921,0.0118,0.0117</t>
-  </si>
-  <si>
-    <t>0.6450,0.1336,0.0141,0.0437</t>
-  </si>
-  <si>
-    <t>0.7506,0.0405,0.0087,0.0594</t>
-  </si>
-  <si>
-    <t>0.8984,0.0195,0.0096,0.0287</t>
-  </si>
-  <si>
-    <t>0.8054,0.0179,0.0315,0.1168</t>
-  </si>
-  <si>
-    <t>0.9395,0.0108,0.0153,0.0109</t>
-  </si>
-  <si>
-    <t>0.8619,0.0224,0.0782,0.0196</t>
-  </si>
-  <si>
-    <t>0.7939,0.0364,0.0277,0.0594</t>
-  </si>
-  <si>
-    <t>0.0991,0.3072,0.8619,0.0063</t>
-  </si>
-  <si>
-    <t>0.5729,0.1774,0.2769,0.0107</t>
-  </si>
-  <si>
-    <t>0.8266,0.0232,0.1230,0.0279</t>
-  </si>
-  <si>
-    <t>0.8822,0.0164,0.1005,0.0036</t>
-  </si>
-  <si>
-    <t>0.4150,0.0376,0.6658,0.0046</t>
-  </si>
-  <si>
-    <t>0.6870,0.0757,0.0159,0.0623</t>
-  </si>
-  <si>
-    <t>0.8970,0.0216,0.0019,0.0144</t>
-  </si>
-  <si>
-    <t>0.4982,0.2614,0.0357,0.0402</t>
-  </si>
-  <si>
-    <t>0.7918,0.0543,0.0110,0.0449</t>
-  </si>
-  <si>
-    <t>0.8216,0.0330,0.0066,0.0398</t>
-  </si>
-  <si>
-    <t>0.4045,0.1681,0.0119,0.1006</t>
-  </si>
-  <si>
-    <t>0.9014,0.0450,0.0030,0.0054</t>
-  </si>
-  <si>
-    <t>0.6852,0.1416,0.0277,0.0405</t>
-  </si>
-  <si>
-    <t>0.6936,0.1327,0.0602,0.0773</t>
-  </si>
-  <si>
-    <t>0.8209,0.0593,0.0192,0.0337</t>
-  </si>
-  <si>
-    <t>0.6238,0.1408,0.0203,0.0524</t>
-  </si>
-  <si>
-    <t>0.7201,0.0541,0.2758,0.0057</t>
-  </si>
-  <si>
-    <t>0.0608,0.3744,0.8719,0.0096</t>
-  </si>
-  <si>
-    <t>0.8422,0.0373,0.0544,0.0169</t>
-  </si>
-  <si>
-    <t>0.0585,0.0282,0.9720,0.0003</t>
-  </si>
-  <si>
-    <t>0.7179,0.0134,0.4418,0.0053</t>
-  </si>
-  <si>
-    <t>0.1642,0.0700,0.7823,0.0249</t>
-  </si>
-  <si>
-    <t>0.5853,0.0222,0.5434,0.0051</t>
-  </si>
-  <si>
-    <t>0.6146,0.0440,0.3198,0.0515</t>
-  </si>
-  <si>
-    <t>0.9603,0.0062,0.0037,0.0054</t>
-  </si>
-  <si>
-    <t>0.8921,0.0272,0.0461,0.0136</t>
-  </si>
-  <si>
-    <t>0.8490,0.0148,0.0098,0.0735</t>
-  </si>
-  <si>
-    <t>0.7106,0.0984,0.0106,0.0283</t>
-  </si>
-  <si>
-    <t>0.8480,0.0575,0.0045,0.0132</t>
-  </si>
-  <si>
-    <t>0.6613,0.2300,0.0160,0.0123</t>
-  </si>
-  <si>
-    <t>0.5540,0.2450,0.0102,0.0150</t>
-  </si>
-  <si>
-    <t>0.7640,0.0632,0.0103,0.0412</t>
-  </si>
-  <si>
-    <t>0.6119,0.0671,0.0193,0.1480</t>
-  </si>
-  <si>
-    <t>0.6358,0.1736,0.0092,0.0156</t>
-  </si>
-  <si>
-    <t>0.7626,0.0341,0.0064,0.0626</t>
-  </si>
-  <si>
-    <t>0.6205,0.2105,0.1413,0.0153</t>
-  </si>
-  <si>
-    <t>0.1635,0.0496,0.8933,0.0013</t>
-  </si>
-  <si>
-    <t>0.2004,0.4752,0.6055,0.0301</t>
-  </si>
-  <si>
-    <t>0.8707,0.0128,0.1011,0.0105</t>
-  </si>
-  <si>
-    <t>0.7092,0.0239,0.3313,0.0125</t>
-  </si>
-  <si>
-    <t>0.9107,0.0141,0.0356,0.0182</t>
-  </si>
-  <si>
-    <t>0.6063,0.1444,0.2258,0.0364</t>
-  </si>
-  <si>
-    <t>0.7299,0.0388,0.2034,0.0376</t>
-  </si>
-  <si>
-    <t>0.8636,0.0225,0.0084,0.0454</t>
-  </si>
-  <si>
-    <t>0.7991,0.0607,0.0087,0.0289</t>
-  </si>
-  <si>
-    <t>0.7105,0.0857,0.0389,0.1020</t>
-  </si>
-  <si>
-    <t>0.6820,0.0171,0.0100,0.2574</t>
-  </si>
-  <si>
-    <t>0.9358,0.0055,0.0051,0.0358</t>
-  </si>
-  <si>
-    <t>0.8603,0.0327,0.0058,0.0301</t>
+    <t>0.9718,0.0041,0.0078,0.0106</t>
+  </si>
+  <si>
+    <t>0.0034,0.0013,0.0016,0.9975</t>
+  </si>
+  <si>
+    <t>0.9688,0.0004,0.0003,0.0497</t>
+  </si>
+  <si>
+    <t>0.2717,0.0045,0.0061,0.8526</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0002,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9959,0.0020,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9958,0.0010,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9946,0.0007,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.7826,0.0329,0.2231,0.0040</t>
+  </si>
+  <si>
+    <t>0.4914,0.0116,0.6916,0.0012</t>
+  </si>
+  <si>
+    <t>0.2052,0.0033,0.9107,0.0005</t>
+  </si>
+  <si>
+    <t>0.0706,0.0014,0.9517,0.0019</t>
+  </si>
+  <si>
+    <t>0.9114,0.0213,0.0653,0.0024</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9958,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.0207,0.9729,0.0018,0.0023</t>
+  </si>
+  <si>
+    <t>0.0021,0.9934,0.0124,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9296,0.0057,0.0603,0.0040</t>
+  </si>
+  <si>
+    <t>0.1189,0.0040,0.9226,0.0030</t>
+  </si>
+  <si>
+    <t>0.0009,0.0010,0.9970,0.0016</t>
+  </si>
+  <si>
+    <t>0.0121,0.0086,0.9589,0.0128</t>
+  </si>
+  <si>
+    <t>0.0079,0.0054,0.9881,0.0014</t>
+  </si>
+  <si>
+    <t>0.0093,0.0007,0.9883,0.0018</t>
+  </si>
+  <si>
+    <t>0.0169,0.0029,0.9731,0.0110</t>
+  </si>
+  <si>
+    <t>0.7732,0.3878,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.4349,0.0289,0.6422,0.0104</t>
+  </si>
+  <si>
+    <t>0.0005,0.0152,0.9967,0.0042</t>
+  </si>
+  <si>
+    <t>0.0231,0.9212,0.0954,0.0027</t>
+  </si>
+  <si>
+    <t>0.9887,0.0026,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.4760,0.0051,0.3813,0.0707</t>
+  </si>
+  <si>
+    <t>0.8684,0.1867,0.0066,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.9913,0.2428,0.0007</t>
+  </si>
+  <si>
+    <t>0.0255,0.7207,0.4782,0.0053</t>
+  </si>
+  <si>
+    <t>0.0976,0.0012,0.8627,0.0119</t>
+  </si>
+  <si>
+    <t>0.0274,0.0129,0.9672,0.0058</t>
+  </si>
+  <si>
+    <t>0.6641,0.0037,0.5693,0.0014</t>
+  </si>
+  <si>
+    <t>0.0054,0.0297,0.9872,0.0025</t>
+  </si>
+  <si>
+    <t>0.0078,0.9794,0.0118,0.0020</t>
+  </si>
+  <si>
+    <t>0.1163,0.0009,0.9325,0.0011</t>
+  </si>
+  <si>
+    <t>0.2181,0.0857,0.0050,0.7259</t>
+  </si>
+  <si>
+    <t>0.0082,0.9761,0.0136,0.0129</t>
+  </si>
+  <si>
+    <t>0.0018,0.9907,0.0273,0.0029</t>
+  </si>
+  <si>
+    <t>0.0007,0.9932,0.0020,0.0029</t>
+  </si>
+  <si>
+    <t>0.0006,0.0391,0.9904,0.0040</t>
+  </si>
+  <si>
+    <t>0.0041,0.1213,0.9844,0.0015</t>
+  </si>
+  <si>
+    <t>0.0185,0.0043,0.9851,0.0004</t>
+  </si>
+  <si>
+    <t>0.0031,0.0006,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0042,0.0027,0.9900,0.0049</t>
+  </si>
+  <si>
+    <t>0.0106,0.1886,0.9650,0.0007</t>
+  </si>
+  <si>
+    <t>0.9905,0.0061,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9938,0.0006,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.9761,0.0053,0.0077,0.0094</t>
+  </si>
+  <si>
+    <t>0.0048,0.0106,0.9938,0.0028</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0012,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9705,0.0308,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9490,0.9922,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0763,0.9938,0.0008</t>
+  </si>
+  <si>
+    <t>0.0027,0.0013,0.9955,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.8227,0.9846,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.0016,0.9970,0.0003</t>
+  </si>
+  <si>
+    <t>0.0088,0.9804,0.0063,0.0011</t>
+  </si>
+  <si>
+    <t>0.0042,0.9945,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9157,0.0183,0.1035,0.0043</t>
+  </si>
+  <si>
+    <t>0.0448,0.1088,0.9445,0.0132</t>
+  </si>
+  <si>
+    <t>0.0050,0.0078,0.9885,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9937,0.9334,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9558,0.5583,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9970,0.8545,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9693,0.9112,0.0006</t>
+  </si>
+  <si>
+    <t>0.0059,0.0005,0.0912,0.9514</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.0007,0.9991</t>
+  </si>
+  <si>
+    <t>0.0059,0.0013,0.0003,0.9978</t>
+  </si>
+  <si>
+    <t>0.0049,0.0055,0.0053,0.9948</t>
+  </si>
+  <si>
+    <t>0.0343,0.0007,0.0004,0.9914</t>
+  </si>
+  <si>
+    <t>0.0033,0.0015,0.0021,0.9968</t>
+  </si>
+  <si>
+    <t>0.0004,0.9670,0.9242,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.5019,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.2751,0.9828,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.5474,0.9903,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.9113,0.9748,0.0003</t>
+  </si>
+  <si>
+    <t>0.0055,0.9635,0.1059,0.0007</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9949,0.0017,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0022,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9879,0.0016,0.0004,0.0053</t>
+  </si>
+  <si>
+    <t>0.9958,0.0010,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9886,0.0030,0.0013,0.0041</t>
+  </si>
+  <si>
+    <t>0.9828,0.0044,0.0026,0.0046</t>
+  </si>
+  <si>
+    <t>0.9912,0.0045,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9950,0.0005,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9923,0.0018,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0082,0.0020,0.9807,0.0111</t>
+  </si>
+  <si>
+    <t>0.0594,0.0066,0.9709,0.0007</t>
+  </si>
+  <si>
+    <t>0.9914,0.0009,0.0052,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.0004,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0214,0.9813,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.0127,0.9807,0.0103,0.0015</t>
+  </si>
+  <si>
+    <t>0.0124,0.9810,0.0082,0.0033</t>
+  </si>
+  <si>
+    <t>0.0638,0.9397,0.0021,0.0023</t>
+  </si>
+  <si>
+    <t>0.0067,0.9905,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9972,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.8364,0.2436,0.0089,0.0015</t>
+  </si>
+  <si>
+    <t>0.7985,0.0596,0.0691,0.0206</t>
+  </si>
+  <si>
+    <t>0.1987,0.0246,0.7824,0.0215</t>
+  </si>
+  <si>
+    <t>0.5510,0.0558,0.3476,0.0488</t>
+  </si>
+  <si>
+    <t>0.4890,0.0174,0.5711,0.0035</t>
+  </si>
+  <si>
+    <t>0.0442,0.0294,0.0282,0.9579</t>
+  </si>
+  <si>
+    <t>0.0030,0.9929,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.0034,0.9886,0.0027,0.0081</t>
+  </si>
+  <si>
+    <t>0.0015,0.9927,0.0047,0.0049</t>
+  </si>
+  <si>
+    <t>0.0003,0.8910,0.9831,0.0002</t>
+  </si>
+  <si>
+    <t>0.0218,0.9810,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.5166,0.5877,0.0080,0.0039</t>
+  </si>
+  <si>
+    <t>0.9306,0.1044,0.0031,0.0016</t>
+  </si>
+  <si>
+    <t>0.9844,0.0074,0.0020,0.0016</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0001,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9953,0.0002,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9951,0.0002,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9910,0.0018,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.9964,0.0002,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.0033,0.4904,0.9768,0.0012</t>
+  </si>
+  <si>
+    <t>0.0076,0.8165,0.5734,0.0009</t>
+  </si>
+  <si>
+    <t>0.0069,0.0328,0.9810,0.0002</t>
+  </si>
+  <si>
+    <t>0.0066,0.0182,0.9815,0.0007</t>
+  </si>
+  <si>
+    <t>0.9872,0.0024,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.9852,0.0014,0.0098,0.0004</t>
+  </si>
+  <si>
+    <t>0.1085,0.0014,0.9310,0.0052</t>
+  </si>
+  <si>
+    <t>0.8013,0.0128,0.2096,0.0105</t>
+  </si>
+  <si>
+    <t>0.0197,0.0007,0.0154,0.9778</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.0028,0.9990</t>
+  </si>
+  <si>
+    <t>0.0006,0.0106,0.0007,0.9990</t>
+  </si>
+  <si>
+    <t>0.0028,0.0001,0.0006,0.9985</t>
+  </si>
+  <si>
+    <t>0.0007,0.9640,0.5944,0.0070</t>
+  </si>
+  <si>
+    <t>0.9950,0.0011,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.1516,0.8302,0.0086,0.0181</t>
+  </si>
+  <si>
+    <t>0.9778,0.0056,0.0152,0.0031</t>
+  </si>
+  <si>
+    <t>0.5231,0.5430,0.0142,0.0067</t>
+  </si>
+  <si>
+    <t>0.9875,0.0021,0.0026,0.0034</t>
+  </si>
+  <si>
+    <t>0.9610,0.0012,0.0049,0.0334</t>
+  </si>
+  <si>
+    <t>0.9942,0.0006,0.0011,0.0026</t>
+  </si>
+  <si>
+    <t>0.0002,0.2127,0.9935,0.0070</t>
+  </si>
+  <si>
+    <t>0.9250,0.0019,0.0042,0.0885</t>
+  </si>
+  <si>
+    <t>0.8831,0.0015,0.0007,0.1881</t>
+  </si>
+  <si>
+    <t>0.2301,0.7650,0.0370,0.0202</t>
+  </si>
+  <si>
+    <t>0.9907,0.0029,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9641,0.0146,0.0121,0.0014</t>
+  </si>
+  <si>
+    <t>0.1811,0.6182,0.1535,0.0199</t>
+  </si>
+  <si>
+    <t>0.9428,0.0243,0.0211,0.0027</t>
+  </si>
+  <si>
+    <t>0.8870,0.1000,0.0088,0.0129</t>
+  </si>
+  <si>
+    <t>0.9891,0.0010,0.0063,0.0016</t>
+  </si>
+  <si>
+    <t>0.9915,0.0003,0.0004,0.0072</t>
+  </si>
+  <si>
+    <t>0.9918,0.0019,0.0030,0.0013</t>
+  </si>
+  <si>
+    <t>0.9961,0.0002,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9904,0.0021,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.9917,0.0010,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.9893,0.0004,0.0042,0.0027</t>
+  </si>
+  <si>
+    <t>0.9629,0.0374,0.0031,0.0011</t>
+  </si>
+  <si>
+    <t>0.8790,0.1958,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.8445,0.2758,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.7446,0.2724,0.0282,0.0133</t>
+  </si>
+  <si>
+    <t>0.9720,0.0258,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.8967,0.0718,0.0466,0.0040</t>
+  </si>
+  <si>
+    <t>0.9931,0.0035,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9058,0.1054,0.0055,0.0080</t>
+  </si>
+  <si>
+    <t>0.0003,0.0677,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.8586,0.0424,0.0884,0.0049</t>
+  </si>
+  <si>
+    <t>0.0042,0.0040,0.9924,0.0028</t>
+  </si>
+  <si>
+    <t>0.0111,0.0109,0.9808,0.0104</t>
+  </si>
+  <si>
+    <t>0.0094,0.0034,0.9876,0.0030</t>
+  </si>
+  <si>
+    <t>0.0109,0.0209,0.9694,0.0036</t>
+  </si>
+  <si>
+    <t>0.0194,0.0188,0.9827,0.0009</t>
+  </si>
+  <si>
+    <t>0.0227,0.0008,0.9899,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0019,0.9937,0.0034</t>
+  </si>
+  <si>
+    <t>0.0028,0.0040,0.9938,0.0007</t>
+  </si>
+  <si>
+    <t>0.3158,0.0283,0.6961,0.0064</t>
+  </si>
+  <si>
+    <t>0.7437,0.0117,0.3923,0.0030</t>
+  </si>
+  <si>
+    <t>0.1105,0.2214,0.5350,0.0093</t>
+  </si>
+  <si>
+    <t>0.1709,0.1272,0.6599,0.0034</t>
+  </si>
+  <si>
+    <t>0.7965,0.0340,0.1718,0.0044</t>
+  </si>
+  <si>
+    <t>0.2368,0.0109,0.7481,0.0268</t>
+  </si>
+  <si>
+    <t>0.1903,0.0997,0.7420,0.0143</t>
+  </si>
+  <si>
+    <t>0.0375,0.9669,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.2631,0.8139,0.0081,0.0024</t>
+  </si>
+  <si>
+    <t>0.9111,0.1729,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9677,0.0278,0.0011,0.0031</t>
+  </si>
+  <si>
+    <t>0.9497,0.0912,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.6005,0.3742,0.0318,0.0052</t>
+  </si>
+  <si>
+    <t>0.9885,0.0012,0.0085,0.0004</t>
+  </si>
+  <si>
+    <t>0.9725,0.0040,0.0139,0.0027</t>
+  </si>
+  <si>
+    <t>0.4768,0.0427,0.4663,0.0341</t>
+  </si>
+  <si>
+    <t>0.9867,0.0021,0.0074,0.0004</t>
+  </si>
+  <si>
+    <t>0.0031,0.0124,0.9873,0.0063</t>
+  </si>
+  <si>
+    <t>0.0203,0.0949,0.9378,0.0050</t>
+  </si>
+  <si>
+    <t>0.0814,0.0090,0.9337,0.0051</t>
+  </si>
+  <si>
+    <t>0.0506,0.0483,0.9211,0.0026</t>
+  </si>
+  <si>
+    <t>0.0067,0.1281,0.9722,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0001,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9890,0.0043,0.0018,0.0024</t>
+  </si>
+  <si>
+    <t>0.9926,0.0020,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9949,0.0018,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9648,0.0340,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9789,0.0014,0.0007,0.0186</t>
+  </si>
+  <si>
+    <t>0.9949,0.0007,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.0261,0.0120,0.9735,0.0029</t>
+  </si>
+  <si>
+    <t>0.0984,0.0584,0.8849,0.0059</t>
+  </si>
+  <si>
+    <t>0.7089,0.0129,0.2849,0.0274</t>
+  </si>
+  <si>
+    <t>0.0034,0.0053,0.9959,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.0037,0.9871,0.0167</t>
+  </si>
+  <si>
+    <t>0.0101,0.0241,0.9756,0.0053</t>
+  </si>
+  <si>
+    <t>0.0048,0.0014,0.9945,0.0006</t>
+  </si>
+  <si>
+    <t>0.0047,0.0034,0.9917,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.0088,0.9808,0.0083</t>
+  </si>
+  <si>
+    <t>0.0291,0.0222,0.9255,0.0088</t>
+  </si>
+  <si>
+    <t>0.5654,0.0032,0.4366,0.0271</t>
+  </si>
+  <si>
+    <t>0.7883,0.0012,0.4088,0.0009</t>
+  </si>
+  <si>
+    <t>0.9798,0.0005,0.0214,0.0008</t>
+  </si>
+  <si>
+    <t>0.9865,0.0087,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9940,0.0024,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9946,0.0010,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.9898,0.0047,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9935,0.0011,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9901,0.0027,0.0017,0.0023</t>
+  </si>
+  <si>
+    <t>0.9668,0.0431,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9947,0.0003,0.0000,0.0029</t>
+  </si>
+  <si>
+    <t>0.0309,0.0716,0.8769,0.0028</t>
+  </si>
+  <si>
+    <t>0.0024,0.0128,0.9867,0.0019</t>
+  </si>
+  <si>
+    <t>0.0045,0.0145,0.9872,0.0053</t>
+  </si>
+  <si>
+    <t>0.0294,0.0121,0.9655,0.0021</t>
+  </si>
+  <si>
+    <t>0.0035,0.0008,0.9932,0.0033</t>
+  </si>
+  <si>
+    <t>0.0894,0.0099,0.9043,0.0172</t>
+  </si>
+  <si>
+    <t>0.0377,0.0038,0.9583,0.0061</t>
+  </si>
+  <si>
+    <t>0.0189,0.0059,0.9583,0.0195</t>
+  </si>
+  <si>
+    <t>0.8325,0.0003,0.0003,0.4133</t>
+  </si>
+  <si>
+    <t>0.1070,0.0040,0.0007,0.9509</t>
+  </si>
+  <si>
+    <t>0.0487,0.0001,0.0003,0.9900</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.0006,0.9991</t>
+  </si>
+  <si>
+    <t>0.9687,0.0009,0.0010,0.0348</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
